--- a/data/trans_orig/IP07A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A01-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>46129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>61233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>80798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28875</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43166</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52673</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>72592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64666</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63609</t>
+          <t>63128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102033</t>
+          <t>101766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123559</t>
+          <t>123486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44786</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88829</t>
+          <t>88345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>38269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35743</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52995</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>72620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48744</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>42554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58805</t>
+          <t>58837</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81714</t>
+          <t>80964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103891</t>
+          <t>103969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33803</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>50480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71688</t>
+          <t>71177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>93673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146270</t>
+          <t>146117</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>175392</t>
+          <t>175764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161972</t>
+          <t>162715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>193038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>317820</t>
+          <t>318110</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>358970</t>
+          <t>359192</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119226</t>
+          <t>119865</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149360</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131119</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>161865</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>262176</t>
+          <t>259218</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>302540</t>
+          <t>299347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42548</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62107</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>29522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>42807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43859</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63132</t>
+          <t>63386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83450</t>
+          <t>82665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44831</t>
+          <t>45269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47668</t>
+          <t>47064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>65625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87742</t>
+          <t>87622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>63549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44888</t>
+          <t>44487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96458</t>
+          <t>96843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>119496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>40245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65006</t>
+          <t>64778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47229</t>
+          <t>46816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35397</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,47 +5902,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>69264</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>60175</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>79011</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>50,91%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>69264</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>60689</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>78490</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,77 +6098,77 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6057</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8323</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>6,12%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6433</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50657</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72169</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>46497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63216</t>
+          <t>62470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>43993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59458</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95262</t>
+          <t>94884</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118007</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97688</t>
+          <t>96566</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125616</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120006</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>148468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>226121</t>
+          <t>225150</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>265388</t>
+          <t>267728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>173214</t>
+          <t>172786</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>201300</t>
+          <t>202834</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155182</t>
+          <t>153086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>184438</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>337710</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>378456</t>
+          <t>379046</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7590,47 +7590,47 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>30390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67238</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89034</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39160</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47780</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68612</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,85%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>53437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>70335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58173</t>
+          <t>57707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>74510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116880</t>
+          <t>117081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139789</t>
+          <t>139370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>62352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85463</t>
+          <t>84747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>46312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78907</t>
+          <t>79500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98281</t>
+          <t>98799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64660</t>
+          <t>64319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46618</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63897</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86826</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109579</t>
+          <t>109978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>42392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60957</t>
+          <t>60352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47210</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79204</t>
+          <t>77886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101727</t>
+          <t>102413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>167663</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197762</t>
+          <t>196516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>196248</t>
+          <t>195992</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226769</t>
+          <t>227053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>373805</t>
+          <t>373283</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>416407</t>
+          <t>415747</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>134047</t>
+          <t>134553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>165301</t>
+          <t>164623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>112117</t>
+          <t>111323</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142802</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>253596</t>
+          <t>254053</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>297037</t>
+          <t>298391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37683</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>63261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67889</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33672</t>
+          <t>33499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57220</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>30936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53071</t>
+          <t>52913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69969</t>
+          <t>68725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>88346</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111035</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147254</t>
+          <t>145031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175058</t>
+          <t>174505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>41803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85087</t>
+          <t>85902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9757</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75349</t>
+          <t>76309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>104759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>64071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87411</t>
+          <t>86648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148714</t>
+          <t>149263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186374</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69408</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>58704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>43184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61298</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91165</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116034</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45300</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>62753</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>86491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>214613</t>
+          <t>213956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>264072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>258431</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>299842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>481176</t>
+          <t>484370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>548243</t>
+          <t>550631</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>91522</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138487</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>104928</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212721</t>
+          <t>209710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>273963</t>
+          <t>271121</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
